--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/scenario_rank_ic_history.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/scenario_rank_ic_history.xlsx
@@ -2984,7 +2984,7 @@
         <v>32</v>
       </c>
       <c r="D140" s="5">
-        <v>-0.04042190567096288</v>
+        <v>-0.05723978810080276</v>
       </c>
       <c r="E140" s="6">
         <v>72</v>
@@ -3001,7 +3001,7 @@
         <v>32</v>
       </c>
       <c r="D141" s="5">
-        <v>0.1761844661620156</v>
+        <v>0.1391430179454715</v>
       </c>
       <c r="E141" s="6">
         <v>72</v>
@@ -3018,7 +3018,7 @@
         <v>32</v>
       </c>
       <c r="D142" s="5">
-        <v>-0.0166102540426542</v>
+        <v>0.1084483604154313</v>
       </c>
       <c r="E142" s="6">
         <v>72</v>
@@ -3035,7 +3035,7 @@
         <v>32</v>
       </c>
       <c r="D143" s="5">
-        <v>0.09211795748407342</v>
+        <v>0.09706802165623932</v>
       </c>
       <c r="E143" s="6">
         <v>72</v>
@@ -3052,7 +3052,7 @@
         <v>32</v>
       </c>
       <c r="D144" s="5">
-        <v>-0.01509804080424196</v>
+        <v>-0.05569579548915109</v>
       </c>
       <c r="E144" s="6">
         <v>72</v>
@@ -3069,7 +3069,7 @@
         <v>32</v>
       </c>
       <c r="D145" s="5">
-        <v>0.07119829572716857</v>
+        <v>0.03495401633545566</v>
       </c>
       <c r="E145" s="6">
         <v>72</v>
@@ -3086,7 +3086,7 @@
         <v>32</v>
       </c>
       <c r="D146" s="5">
-        <v>-0.03863716759241202</v>
+        <v>-0.01512983358986465</v>
       </c>
       <c r="E146" s="6">
         <v>72</v>
@@ -3103,7 +3103,7 @@
         <v>32</v>
       </c>
       <c r="D147" s="5">
-        <v>0.00453423589648161</v>
+        <v>-0.01485638028522736</v>
       </c>
       <c r="E147" s="6">
         <v>72</v>
@@ -3120,7 +3120,7 @@
         <v>32</v>
       </c>
       <c r="D148" s="5">
-        <v>0.194497596743786</v>
+        <v>0.1598025580680462</v>
       </c>
       <c r="E148" s="6">
         <v>72</v>
@@ -3137,7 +3137,7 @@
         <v>32</v>
       </c>
       <c r="D149" s="5">
-        <v>0.02707896174126358</v>
+        <v>0.04519655921478166</v>
       </c>
       <c r="E149" s="6">
         <v>72</v>
@@ -3154,7 +3154,7 @@
         <v>32</v>
       </c>
       <c r="D150" s="5">
-        <v>0.1253859019830345</v>
+        <v>0.0507279582747283</v>
       </c>
       <c r="E150" s="6">
         <v>72</v>
@@ -3171,7 +3171,7 @@
         <v>32</v>
       </c>
       <c r="D151" s="5">
-        <v>0.2019631961612875</v>
+        <v>0.1944690087878991</v>
       </c>
       <c r="E151" s="6">
         <v>72</v>
@@ -3188,7 +3188,7 @@
         <v>32</v>
       </c>
       <c r="D152" s="5">
-        <v>-0.0007235308305461313</v>
+        <v>0.01430983198191237</v>
       </c>
       <c r="E152" s="6">
         <v>72</v>
@@ -3205,7 +3205,7 @@
         <v>32</v>
       </c>
       <c r="D153" s="5">
-        <v>0.00514514949220699</v>
+        <v>0.02197943548702174</v>
       </c>
       <c r="E153" s="6">
         <v>72</v>
@@ -3222,7 +3222,7 @@
         <v>32</v>
       </c>
       <c r="D154" s="5">
-        <v>0.2074493316893821</v>
+        <v>0.1306043041741362</v>
       </c>
       <c r="E154" s="6">
         <v>72</v>
@@ -3239,7 +3239,7 @@
         <v>32</v>
       </c>
       <c r="D155" s="5">
-        <v>0.05815907333748996</v>
+        <v>0.1245598520942418</v>
       </c>
       <c r="E155" s="6">
         <v>72</v>
@@ -3256,7 +3256,7 @@
         <v>32</v>
       </c>
       <c r="D156" s="5">
-        <v>0.1562851722839138</v>
+        <v>0.200141488198598</v>
       </c>
       <c r="E156" s="6">
         <v>72</v>
@@ -3273,7 +3273,7 @@
         <v>32</v>
       </c>
       <c r="D157" s="5">
-        <v>-0.07412588556423244</v>
+        <v>-0.05220634933564203</v>
       </c>
       <c r="E157" s="6">
         <v>72</v>
@@ -3290,7 +3290,7 @@
         <v>32</v>
       </c>
       <c r="D158" s="5">
-        <v>-0.02503537437645353</v>
+        <v>-0.08873632337031363</v>
       </c>
       <c r="E158" s="6">
         <v>72</v>
@@ -3307,7 +3307,7 @@
         <v>32</v>
       </c>
       <c r="D159" s="5">
-        <v>-0.025323375486183</v>
+        <v>-0.03542085377095838</v>
       </c>
       <c r="E159" s="6">
         <v>72</v>
@@ -3324,7 +3324,7 @@
         <v>32</v>
       </c>
       <c r="D160" s="5">
-        <v>-0.03265667087214982</v>
+        <v>0.00101293501944732</v>
       </c>
       <c r="E160" s="6">
         <v>72</v>
@@ -3341,7 +3341,7 @@
         <v>32</v>
       </c>
       <c r="D161" s="5">
-        <v>0.02500542751473284</v>
+        <v>0.2084013348960777</v>
       </c>
       <c r="E161" s="6">
         <v>72</v>
@@ -3358,7 +3358,7 @@
         <v>32</v>
       </c>
       <c r="D162" s="5">
-        <v>-0.08037946710481386</v>
+        <v>-0.02497005362936705</v>
       </c>
       <c r="E162" s="6">
         <v>72</v>
@@ -3375,7 +3375,7 @@
         <v>33</v>
       </c>
       <c r="D163" s="5">
-        <v>-0.0358386056880647</v>
+        <v>-0.05148241044440158</v>
       </c>
       <c r="E163" s="6">
         <v>72</v>
@@ -3392,7 +3392,7 @@
         <v>33</v>
       </c>
       <c r="D164" s="5">
-        <v>0.1779403489256452</v>
+        <v>0.1444787446138016</v>
       </c>
       <c r="E164" s="6">
         <v>72</v>
@@ -3409,7 +3409,7 @@
         <v>33</v>
       </c>
       <c r="D165" s="5">
-        <v>-0.0168499581966686</v>
+        <v>0.1030934465238922</v>
       </c>
       <c r="E165" s="6">
         <v>72</v>
@@ -3426,7 +3426,7 @@
         <v>33</v>
       </c>
       <c r="D166" s="5">
-        <v>0.1283533374642533</v>
+        <v>0.1022582019632533</v>
       </c>
       <c r="E166" s="6">
         <v>72</v>
@@ -3443,7 +3443,7 @@
         <v>33</v>
       </c>
       <c r="D167" s="5">
-        <v>-0.03349116897632964</v>
+        <v>-0.1015820953115956</v>
       </c>
       <c r="E167" s="6">
         <v>72</v>
@@ -3460,7 +3460,7 @@
         <v>33</v>
       </c>
       <c r="D168" s="5">
-        <v>0.05772075374622163</v>
+        <v>-0.003569361373721784</v>
       </c>
       <c r="E168" s="6">
         <v>72</v>
@@ -3477,7 +3477,7 @@
         <v>33</v>
       </c>
       <c r="D169" s="5">
-        <v>-0.01775048034079113</v>
+        <v>-0.009711235449225031</v>
       </c>
       <c r="E169" s="6">
         <v>72</v>
@@ -3494,7 +3494,7 @@
         <v>33</v>
       </c>
       <c r="D170" s="5">
-        <v>0.0007074466802489219</v>
+        <v>-0.03234934722490193</v>
       </c>
       <c r="E170" s="6">
         <v>72</v>
@@ -3511,7 +3511,7 @@
         <v>33</v>
       </c>
       <c r="D171" s="5">
-        <v>0.2230225659484726</v>
+        <v>0.1487555469805132</v>
       </c>
       <c r="E171" s="6">
         <v>72</v>
@@ -3528,7 +3528,7 @@
         <v>33</v>
       </c>
       <c r="D172" s="5">
-        <v>0.005080712586018395</v>
+        <v>0.02022654372166236</v>
       </c>
       <c r="E172" s="6">
         <v>72</v>
@@ -3545,7 +3545,7 @@
         <v>33</v>
       </c>
       <c r="D173" s="5">
-        <v>0.1182069586468583</v>
+        <v>0.02305614508971638</v>
       </c>
       <c r="E173" s="6">
         <v>72</v>
@@ -3562,7 +3562,7 @@
         <v>33</v>
       </c>
       <c r="D174" s="5">
-        <v>0.2023619072184757</v>
+        <v>0.1992909454928497</v>
       </c>
       <c r="E174" s="6">
         <v>72</v>
@@ -3579,7 +3579,7 @@
         <v>33</v>
       </c>
       <c r="D175" s="5">
-        <v>0.02167341951250885</v>
+        <v>-0.0356293009196733</v>
       </c>
       <c r="E175" s="6">
         <v>72</v>
@@ -3596,7 +3596,7 @@
         <v>33</v>
       </c>
       <c r="D176" s="5">
-        <v>-0.01594957875104509</v>
+        <v>-0.1396552832979613</v>
       </c>
       <c r="E176" s="6">
         <v>72</v>
@@ -3613,7 +3613,7 @@
         <v>33</v>
       </c>
       <c r="D177" s="5">
-        <v>0.1503312110103544</v>
+        <v>0.1296867965785581</v>
       </c>
       <c r="E177" s="6">
         <v>72</v>
@@ -3630,7 +3630,7 @@
         <v>33</v>
       </c>
       <c r="D178" s="5">
-        <v>0.04804167470576887</v>
+        <v>0.1257958711171137</v>
       </c>
       <c r="E178" s="6">
         <v>72</v>
@@ -3647,7 +3647,7 @@
         <v>33</v>
       </c>
       <c r="D179" s="5">
-        <v>0.06952215576564409</v>
+        <v>0.1069843719853367</v>
       </c>
       <c r="E179" s="6">
         <v>72</v>
@@ -3664,7 +3664,7 @@
         <v>33</v>
       </c>
       <c r="D180" s="5">
-        <v>0.002733294745642807</v>
+        <v>-0.02267026818444916</v>
       </c>
       <c r="E180" s="6">
         <v>72</v>
@@ -3681,7 +3681,7 @@
         <v>33</v>
       </c>
       <c r="D181" s="5">
-        <v>0.05386198469354943</v>
+        <v>-0.01865071708791562</v>
       </c>
       <c r="E181" s="6">
         <v>72</v>
@@ -3698,7 +3698,7 @@
         <v>33</v>
       </c>
       <c r="D182" s="5">
-        <v>-0.01787896327738119</v>
+        <v>0.008199884236928421</v>
       </c>
       <c r="E182" s="6">
         <v>72</v>
@@ -3715,7 +3715,7 @@
         <v>33</v>
       </c>
       <c r="D183" s="5">
-        <v>0.1043153900572384</v>
+        <v>0.08730464981670848</v>
       </c>
       <c r="E183" s="6">
         <v>72</v>
@@ -3732,7 +3732,7 @@
         <v>33</v>
       </c>
       <c r="D184" s="5">
-        <v>-0.02363496044761721</v>
+        <v>0.06508457135507108</v>
       </c>
       <c r="E184" s="6">
         <v>72</v>
@@ -3749,7 +3749,7 @@
         <v>33</v>
       </c>
       <c r="D185" s="5">
-        <v>-0.01874718631423243</v>
+        <v>-0.05579136921988553</v>
       </c>
       <c r="E185" s="6">
         <v>72</v>
